--- a/data/trans_orig/P21D5_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D5_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psiquiatra) en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psiquiatra) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>182567</t>
+          <t>183496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118588</t>
+          <t>117851</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137696</t>
+          <t>137576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>312833</t>
+          <t>312571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>337947</t>
+          <t>338036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>20453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28245</t>
+          <t>28583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2688</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13437</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>2688</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13341</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>13809</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2688</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>15707</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>183547</t>
+          <t>181906</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>201569</t>
+          <t>201525</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>282257</t>
+          <t>281718</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>290370</t>
+          <t>290530</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>469941</t>
+          <t>469326</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>490588</t>
+          <t>490358</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19792</t>
+          <t>20904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24028</t>
+          <t>23907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1638,97 +1638,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2689</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>924</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>4736</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5832</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>4448</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198495</t>
+          <t>197662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211699</t>
+          <t>211703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>236158</t>
+          <t>235697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248754</t>
+          <t>248351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>438267</t>
+          <t>439789</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>455978</t>
+          <t>457322</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>14255</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>33130</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4354</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>880</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4695</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4425</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>880</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5265</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -2207,97 +2207,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3246</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4456</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3906</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3758</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79580</t>
+          <t>81788</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>487129</t>
+          <t>486076</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>296573</t>
+          <t>295852</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>308888</t>
+          <t>308794</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>249764</t>
+          <t>263350</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>793837</t>
+          <t>792179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30704</t>
+          <t>32206</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>445323</t>
+          <t>444576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7687</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>19498</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39599</t>
+          <t>40642</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>602499</t>
+          <t>577899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>15868</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>209717</t>
+          <t>210616</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>226302</t>
+          <t>226330</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>195853</t>
+          <t>195933</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>209444</t>
+          <t>209624</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>411069</t>
+          <t>412427</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>432297</t>
+          <t>433174</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,12%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13758</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25922</t>
+          <t>25770</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25383</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44274</t>
+          <t>43345</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>149189</t>
+          <t>149398</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>155504</t>
+          <t>155573</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>165235</t>
+          <t>165278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175464</t>
+          <t>175281</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>317918</t>
+          <t>317394</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>329261</t>
+          <t>329445</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>482</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>19454</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>110624</t>
+          <t>110631</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>116748</t>
+          <t>116667</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>159119</t>
+          <t>159268</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>166309</t>
+          <t>166338</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>271839</t>
+          <t>272770</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>281703</t>
+          <t>281880</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>920</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,62 +4518,62 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>816973</t>
+          <t>838681</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1581966</t>
+          <t>1584973</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1486961</t>
+          <t>1486267</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1519843</t>
+          <t>1519465</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2174383</t>
+          <t>2184149</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3085632</t>
+          <t>3086476</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>67168</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>848528</t>
+          <t>817950</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>53876</t>
+          <t>54084</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>82288</t>
+          <t>81291</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>133881</t>
+          <t>134421</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1054898</t>
+          <t>1045858</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>17882</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>23924</t>
+          <t>24159</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>15835</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>38711</t>
+          <t>37149</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D5_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D5_2023-Edad-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>197656</t>
+          <t>204840</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>183496</t>
+          <t>190951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>131817</t>
+          <t>153889</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117851</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137576</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>329472</t>
+          <t>358729</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>312571</t>
+          <t>340977</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>338036</t>
+          <t>367568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20453</t>
+          <t>19830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>19407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28583</t>
+          <t>30444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>195216</t>
+          <t>215924</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>181906</t>
+          <t>203501</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>201525</t>
+          <t>222152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>287662</t>
+          <t>246717</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>281718</t>
+          <t>241348</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>290530</t>
+          <t>249370</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>482878</t>
+          <t>462640</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>469326</t>
+          <t>449573</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>490358</t>
+          <t>469810</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23907</t>
+          <t>23779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>928</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>987</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>987</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>206154</t>
+          <t>242980</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197662</t>
+          <t>234571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211703</t>
+          <t>248405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>243344</t>
+          <t>281034</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>235697</t>
+          <t>273280</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248351</t>
+          <t>286549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>449498</t>
+          <t>524014</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>439789</t>
+          <t>513415</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>457322</t>
+          <t>532153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19450</t>
+          <t>21368</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>23363</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14255</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>33976</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>966</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>966</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>810</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>810</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>257222</t>
+          <t>289267</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81788</t>
+          <t>277233</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>486076</t>
+          <t>298411</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>303219</t>
+          <t>326067</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>295852</t>
+          <t>317913</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>308794</t>
+          <t>332067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>560440</t>
+          <t>615334</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>263350</t>
+          <t>602826</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>792179</t>
+          <t>627118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>264020</t>
+          <t>21232</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32206</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>444576</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19498</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>276179</t>
+          <t>35353</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40642</t>
+          <t>25963</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>577899</t>
+          <t>46749</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,67 +2693,67 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>4462</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>15157</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>8189</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>2508</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>15868</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>526394</t>
+          <t>315912</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>526394</t>
+          <t>315912</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>526394</t>
+          <t>315912</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>847256</t>
+          <t>661720</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>847256</t>
+          <t>661720</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>847256</t>
+          <t>661720</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>219211</t>
+          <t>237832</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>210616</t>
+          <t>228142</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>226330</t>
+          <t>244185</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>203722</t>
+          <t>228756</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>195933</t>
+          <t>220910</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>209624</t>
+          <t>235349</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>422934</t>
+          <t>466588</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>412427</t>
+          <t>454465</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>433174</t>
+          <t>476120</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>15364</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>20704</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25770</t>
+          <t>27899</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>34053</t>
+          <t>36068</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24804</t>
+          <t>27154</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43345</t>
+          <t>47048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3350,92 +3350,92 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5154</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>3616</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>8544</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>5058</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>3543</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>8792</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>153541</t>
+          <t>170895</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>149398</t>
+          <t>166199</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>155573</t>
+          <t>173145</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>170856</t>
+          <t>182932</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>165278</t>
+          <t>176662</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175281</t>
+          <t>187825</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>324398</t>
+          <t>353828</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>317394</t>
+          <t>346628</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>329445</t>
+          <t>359596</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>493</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>18226</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>14691</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19454</t>
+          <t>20849</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>385</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>114684</t>
+          <t>126079</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>110631</t>
+          <t>122258</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>116667</t>
+          <t>128228</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>163312</t>
+          <t>178695</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>159268</t>
+          <t>173446</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>166338</t>
+          <t>182008</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>277997</t>
+          <t>304774</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>272770</t>
+          <t>299670</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>281880</t>
+          <t>309417</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>528</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1343683</t>
+          <t>1487816</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>838681</t>
+          <t>1464914</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1584973</t>
+          <t>1505429</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1503933</t>
+          <t>1598089</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1486267</t>
+          <t>1580219</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1519465</t>
+          <t>1613685</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>2847617</t>
+          <t>3085905</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2184149</t>
+          <t>3059035</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3086476</t>
+          <t>3108915</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>306874</t>
+          <t>65745</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>65094</t>
+          <t>49074</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>817950</t>
+          <t>88048</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>67498</t>
+          <t>74456</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>54084</t>
+          <t>61539</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>81291</t>
+          <t>89425</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>374372</t>
+          <t>140201</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>134421</t>
+          <t>119216</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1045858</t>
+          <t>167189</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,67 +4969,67 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24159</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>25322</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>16975</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>36487</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>24340</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>15669</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>37149</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5047,67 +5047,67 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>12548</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>2979</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>11657</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
